--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487935_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487935_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6493</v>
+        <v>4.2295</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7589</v>
+        <v>3.5445</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8905</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>3.4972</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1116</v>
+        <v>-0.3083</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3882</v>
+        <v>0.1738</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2766</v>
+        <v>-0.4821</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8956</v>
+        <v>3.4838</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8944</v>
+        <v>2.4238</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0012</v>
+        <v>1.0599</v>
       </c>
       <c r="G3" t="n">
         <v>1.5911</v>
@@ -688,13 +688,13 @@
         <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0137</v>
+        <v>-0.4255</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7887</v>
+        <v>0.3182</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8024</v>
+        <v>-0.7437</v>
       </c>
       <c r="V3" t="n">
         <v>0.237</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4943</v>
+        <v>3.167</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7218</v>
+        <v>3.0204</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7725</v>
+        <v>0.1466</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0761</v>
+        <v>0.5956</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3135</v>
+        <v>-2.608</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3896</v>
+        <v>3.2036</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2966</v>
+        <v>1.8612</v>
       </c>
       <c r="K4" t="n">
-        <v>0.552</v>
+        <v>-1.9792</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7446</v>
+        <v>3.8404</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2206</v>
+        <v>-1.2656</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8655</v>
+        <v>-0.6288</v>
       </c>
       <c r="O4" t="n">
-        <v>0.645</v>
+        <v>-0.6368</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0812</v>
+        <v>2.9137</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.67</v>
+        <v>-0.3743</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5748</v>
+        <v>-0.1571</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.2172</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0071</v>
+        <v>1.2807</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0071</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3833</v>
+        <v>3.0175</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3541</v>
+        <v>1.2157</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0291</v>
+        <v>1.8018</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5956</v>
+        <v>1.0761</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.608</v>
+        <v>-0.3135</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2036</v>
+        <v>1.3896</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8612</v>
+        <v>1.2966</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9792</v>
+        <v>0.552</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8404</v>
+        <v>0.7446</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2656</v>
+        <v>-0.2206</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6288</v>
+        <v>-0.8655</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6368</v>
+        <v>0.645</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9137</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.158</v>
+        <v>-0.1468</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8234</v>
+        <v>-0.0809</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3346</v>
+        <v>-0.0659</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2807</v>
+        <v>0.0071</v>
       </c>
       <c r="W5" t="n">
-        <v>2.565</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2843</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4665</v>
+        <v>1.1872</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.0044</v>
+        <v>-2.2543</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4709</v>
+        <v>3.4416</v>
       </c>
       <c r="G6" t="n">
         <v>-1.9494</v>
@@ -922,13 +922,13 @@
         <v>2.9137</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7993</v>
+        <v>-1.0786</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1496</v>
+        <v>-0.3995</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.6791</v>
       </c>
       <c r="V6" t="n">
         <v>2.3421</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1783</v>
+        <v>-0.666</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6452</v>
+        <v>-3.1186</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4669</v>
+        <v>2.4526</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6586</v>
+        <v>-0.8901</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1237</v>
+        <v>-1.6992</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5349</v>
+        <v>0.8091</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6339</v>
+        <v>-1.3308</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2642</v>
+        <v>-1.352</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8981</v>
+        <v>0.0212</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0247</v>
+        <v>0.4407</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3879</v>
+        <v>-0.3472</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6368</v>
+        <v>0.7879</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="S7" t="n">
-        <v>1.143</v>
+        <v>-0.1297</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3602</v>
+        <v>0.0634</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2172</v>
+        <v>-0.193</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3467</v>
+        <v>0.3538</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5142</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3304</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0212</v>
+        <v>-1.4499</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6909</v>
+        <v>0.779</v>
       </c>
       <c r="G8" t="n">
         <v>2.2512</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5004</v>
+        <v>-0.8409</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4534</v>
+        <v>0.0248</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9538</v>
+        <v>-0.8657</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5656</v>
+        <v>-0.8699</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4736</v>
+        <v>-0.4031</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.092</v>
+        <v>-0.4669</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4894</v>
+        <v>-1.6586</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3389</v>
+        <v>-0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1505</v>
+        <v>-1.5349</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4481</v>
+        <v>-0.6339</v>
       </c>
       <c r="K9" t="n">
-        <v>0.245</v>
+        <v>0.2642</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6932</v>
+        <v>-0.8981</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0412</v>
+        <v>-1.0247</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5839</v>
+        <v>-0.3879</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4573</v>
+        <v>-0.6368</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-1.2487</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8731</v>
+        <v>2.2893</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4867</v>
+        <v>0.0948</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6582</v>
+        <v>0.312</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1715</v>
+        <v>-0.2172</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6452</v>
+        <v>-0.3467</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2477</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6851</v>
+        <v>-0.9584</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2258</v>
+        <v>-0.837</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5407</v>
+        <v>-0.1214</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8901</v>
+        <v>-2.4894</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6992</v>
+        <v>-0.3389</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8091</v>
+        <v>-2.1505</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3308</v>
+        <v>-0.4481</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.352</v>
+        <v>0.245</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0212</v>
+        <v>-0.6932</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4407</v>
+        <v>-2.0412</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3472</v>
+        <v>-0.5839</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7879</v>
+        <v>-1.4573</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1487</v>
+        <v>0.0939</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0438</v>
+        <v>0.2948</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.105</v>
+        <v>-0.2009</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3538</v>
+        <v>1.6452</v>
       </c>
       <c r="W10" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1238</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>G. VERGARA HARBOE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6689</v>
+        <v>-1.1908</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4965</v>
+        <v>-0.4262</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1724</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7014</v>
+        <v>1.2489</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1771</v>
+        <v>1.8229</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-0.5739</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1559</v>
+        <v>2.1756</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0384</v>
+        <v>1.6842</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1176</v>
+        <v>0.4915</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8573</v>
+        <v>-0.9267</v>
       </c>
       <c r="N11" t="n">
         <v>0.1387</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.996</v>
+        <v>-1.0654</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6244</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1944</v>
+        <v>0.0171</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4443</v>
+        <v>0.1443</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2499</v>
+        <v>-0.1272</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3975</v>
+        <v>-0.5838</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. VERGARA HARBOE</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9745</v>
+        <v>-1.2338</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0924</v>
+        <v>-0.0026</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.882</v>
+        <v>-1.2311</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2489</v>
+        <v>-0.7014</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8229</v>
+        <v>0.1771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5739</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1756</v>
+        <v>0.1559</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6842</v>
+        <v>0.0384</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4915</v>
+        <v>0.1176</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9267</v>
+        <v>-0.8573</v>
       </c>
       <c r="N12" t="n">
         <v>0.1387</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0654</v>
+        <v>-0.996</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.3299</v>
+        <v>-0.2081</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7665999999999999</v>
+        <v>0.2407</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5219</v>
+        <v>0.0496</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2446</v>
+        <v>0.1912</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5838</v>
+        <v>-1.3975</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.842799999999997</v>
+        <v>9.495200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.060499999999998</v>
+        <v>1.712700000000001</v>
       </c>
       <c r="F13" t="n">
         <v>7.782500000000001</v>
@@ -1441,16 +1441,16 @@
         <v>9.980699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>6.6751</v>
+        <v>6.675099999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.979100000000001</v>
+        <v>-3.9791</v>
       </c>
       <c r="L13" t="n">
         <v>10.6542</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.1039</v>
+        <v>-4.103899999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-3.4304</v>
@@ -1468,13 +1468,13 @@
         <v>20.812</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.509799999999999</v>
+        <v>-2.8576</v>
       </c>
       <c r="T13" t="n">
-        <v>0.09089999999999998</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.6007</v>
+        <v>-3.6008</v>
       </c>
       <c r="V13" t="n">
         <v>3.5379</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>B. AREVALO SAENZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4953</v>
+        <v>3.885</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1906</v>
+        <v>2.4286</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3047</v>
+        <v>1.4564</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8487</v>
+        <v>1.8897</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3517</v>
+        <v>2.2155</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.503</v>
+        <v>-0.3257</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6693</v>
+        <v>2.0736</v>
       </c>
       <c r="K14" t="n">
-        <v>2.217</v>
+        <v>1.7993</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4523</v>
+        <v>0.2743</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8206</v>
+        <v>-0.1839</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1347</v>
+        <v>0.4162</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9553</v>
+        <v>-0.6001</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2054</v>
+        <v>0.0171</v>
       </c>
       <c r="T14" t="n">
-        <v>3.41</v>
+        <v>-0.0019</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7954</v>
+        <v>0.019</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4776</v>
+        <v>0.9376</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2737</v>
+        <v>1.3975</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7513</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. AREVALO SAENZ</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3747</v>
+        <v>1.1222</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3215</v>
+        <v>-1.5401</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0532</v>
+        <v>2.6624</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8897</v>
+        <v>1.123</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2155</v>
+        <v>0.2772</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3257</v>
+        <v>0.8458</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0736</v>
+        <v>-0.1219</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7993</v>
+        <v>-0.1431</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2743</v>
+        <v>0.0212</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1839</v>
+        <v>1.2449</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4162</v>
+        <v>0.4203</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6001</v>
+        <v>0.8246</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4932</v>
+        <v>-0.3952</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.109</v>
+        <v>-0.3776</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3842</v>
+        <v>-0.0176</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9376</v>
+        <v>-0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5904</v>
+        <v>1.0316</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0759</v>
+        <v>0.9403</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6663</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.123</v>
+        <v>1.8487</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2772</v>
+        <v>3.3517</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8458</v>
+        <v>-1.503</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1219</v>
+        <v>2.6693</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1431</v>
+        <v>2.217</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0212</v>
+        <v>0.4523</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2449</v>
+        <v>-0.8206</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4203</v>
+        <v>1.1347</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8246</v>
+        <v>-1.9553</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.927</v>
+        <v>1.7418</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9134</v>
+        <v>1.1597</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0136</v>
+        <v>0.582</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.23</v>
+        <v>-0.4776</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2737</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0121</v>
+        <v>0.3906</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8594</v>
+        <v>0.988</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8715</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0926</v>
+        <v>-2.8408</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1131</v>
+        <v>-0.3539</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0204</v>
+        <v>-2.4868</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4218</v>
+        <v>-0.3547</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2258</v>
+        <v>-0.6804</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1959</v>
+        <v>0.3257</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5144</v>
+        <v>-2.4861</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3389</v>
+        <v>0.3265</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1755</v>
+        <v>-2.8126</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4562</v>
+        <v>0.6258</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3106</v>
+        <v>0.402</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1455</v>
+        <v>0.2238</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1675</v>
+        <v>1.9813</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>1.9813</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7166</v>
+        <v>-0.7716</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0236</v>
+        <v>-2.6845</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7402</v>
+        <v>1.9129</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8408</v>
+        <v>1.9974</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3539</v>
+        <v>1.128</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.4868</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3547</v>
+        <v>1.475</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6804</v>
+        <v>0.6096</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3257</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4861</v>
+        <v>0.5224</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3265</v>
+        <v>0.5183</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.8126</v>
+        <v>0.0041</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6244</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4815</v>
+        <v>0.1041</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5624</v>
+        <v>0.0029</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0809</v>
+        <v>0.1012</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9813</v>
+        <v>-0.5838</v>
       </c>
       <c r="W18" t="n">
-        <v>1.9813</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.851</v>
+        <v>-0.8796</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3274</v>
+        <v>1.1093</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4764</v>
+        <v>-1.9889</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9974</v>
+        <v>-0.0926</v>
       </c>
       <c r="H19" t="n">
-        <v>1.128</v>
+        <v>-0.1131</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="J19" t="n">
-        <v>1.475</v>
+        <v>0.4218</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6096</v>
+        <v>0.2258</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.1959</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5224</v>
+        <v>-0.5144</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5183</v>
+        <v>-0.3389</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0041</v>
+        <v>-0.1755</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9752999999999999</v>
+        <v>0.5886</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.64</v>
+        <v>0.5606</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3353</v>
+        <v>0.0281</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5838</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BIRD-JELINEK</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0091</v>
+        <v>-1.7539</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2613</v>
+        <v>-0.8057</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2704</v>
+        <v>-0.9483</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.115</v>
+        <v>-1.0939</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7483</v>
+        <v>1.2345</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3667</v>
+        <v>-2.3284</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2821</v>
+        <v>1.4861</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6952</v>
+        <v>0.8591</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4131</v>
+        <v>0.627</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8329</v>
+        <v>-2.58</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0532</v>
+        <v>0.3755</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7798</v>
+        <v>-2.9554</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6244</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q20" t="n">
+        <v>-3.1218</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.2487</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.2307</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.8478</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.6244</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.6491</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.5434</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.1057</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-1.1675</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>A. BIRD-JELINEK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0818</v>
+        <v>-2.0091</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.02</v>
+        <v>0.2613</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0618</v>
+        <v>-2.2704</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0939</v>
+        <v>-2.115</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2345</v>
+        <v>-0.7483</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3284</v>
+        <v>-1.3667</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4861</v>
+        <v>-0.2821</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8591</v>
+        <v>-0.6952</v>
       </c>
       <c r="L21" t="n">
-        <v>0.627</v>
+        <v>0.4131</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.58</v>
+        <v>-1.8329</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3755</v>
+        <v>-0.0532</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9554</v>
+        <v>-1.7798</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9029</v>
+        <v>0.6491</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6334</v>
+        <v>0.5434</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2695</v>
+        <v>0.1057</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0177</v>
+        <v>-1.1675</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0177</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4807</v>
+        <v>-3.937</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.398</v>
+        <v>-4.2908</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0827</v>
+        <v>0.3538</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6569</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2857</v>
+        <v>0.2579</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3477</v>
+        <v>0.4548</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6334</v>
+        <v>-0.197</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1519</v>
+        <v>-4.4924</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6176</v>
+        <v>-4.189</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5344</v>
+        <v>-0.3034</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6309</v>
@@ -2248,13 +2248,13 @@
         <v>1.8731</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5409</v>
+        <v>0.1187</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4195</v>
+        <v>0.0091</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1213</v>
+        <v>0.1096</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8127</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.8428</v>
+        <v>-7.414199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.7825</v>
+        <v>-7.7826</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0604</v>
+        <v>0.3685000000000003</v>
       </c>
       <c r="G24" t="n">
         <v>-2.571300000000001</v>
@@ -2296,10 +2296,10 @@
         <v>7.4096</v>
       </c>
       <c r="I24" t="n">
-        <v>-9.980700000000001</v>
+        <v>-9.980699999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>4.103999999999999</v>
+        <v>4.103999999999998</v>
       </c>
       <c r="K24" t="n">
         <v>3.4306</v>
@@ -2326,13 +2326,13 @@
         <v>14.5684</v>
       </c>
       <c r="S24" t="n">
-        <v>3.51</v>
+        <v>4.938599999999999</v>
       </c>
       <c r="T24" t="n">
         <v>3.6008</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.09079999999999981</v>
+        <v>1.3378</v>
       </c>
       <c r="V24" t="n">
         <v>-3.5379</v>
